--- a/pandas/employees.xlsx
+++ b/pandas/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\P01_Learning Services\Prudentia\gitexamples\kaiserrepo\pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070866DE-5411-4599-AEAE-1024D2855000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75B93FD-DE48-4267-A7C1-AD0EB616F9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1385AB81-CCA4-4676-9FF2-B72CAFE4285E}"/>
   </bookViews>
@@ -3339,6 +3339,7 @@
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
